--- a/data-raw/metadata/KDL_project_metadata.xlsx
+++ b/data-raw/metadata/KDL_project_metadata.xlsx
@@ -973,7 +973,7 @@
         <v>57</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45764</v>
+        <v>45982</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/metadata/KDL_project_metadata.xlsx
+++ b/data-raw/metadata/KDL_project_metadata.xlsx
@@ -973,7 +973,7 @@
         <v>57</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45982</v>
+        <v>46047</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/metadata/KDL_project_metadata.xlsx
+++ b/data-raw/metadata/KDL_project_metadata.xlsx
@@ -973,7 +973,7 @@
         <v>57</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46047</v>
+        <v>46151</v>
       </c>
     </row>
   </sheetData>
